--- a/hasil_open_close_total.xlsx
+++ b/hasil_open_close_total.xlsx
@@ -438,13 +438,13 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="E2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
@@ -458,13 +458,13 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
@@ -478,13 +478,13 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D4">
-        <v>367</v>
+        <v>241</v>
       </c>
       <c r="E4">
-        <v>436</v>
+        <v>317</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
@@ -498,13 +498,13 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
@@ -518,13 +518,13 @@
         <v>64</v>
       </c>
       <c r="C6">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="D6">
-        <v>1490</v>
+        <v>983</v>
       </c>
       <c r="E6">
-        <v>1670</v>
+        <v>1149</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -538,13 +538,13 @@
         <v>64</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -558,13 +558,13 @@
         <v>128</v>
       </c>
       <c r="C8">
-        <v>417</v>
+        <v>379</v>
       </c>
       <c r="D8">
-        <v>6005</v>
+        <v>3979</v>
       </c>
       <c r="E8">
-        <v>6422</v>
+        <v>4358</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
@@ -578,13 +578,13 @@
         <v>128</v>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
